--- a/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
@@ -537,22 +537,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -569,22 +572,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -601,22 +607,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>11.43</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -633,22 +642,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -665,22 +677,25 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -697,22 +712,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.5</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -729,22 +747,25 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>17.24</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -761,22 +782,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -793,22 +817,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>3.45</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -825,22 +852,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2018,22 +2048,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2050,22 +2083,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2082,22 +2118,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>11.43</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2114,22 +2153,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2146,22 +2188,25 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2178,22 +2223,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.5</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2210,22 +2258,25 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>17.24</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2242,22 +2293,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2274,22 +2328,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>3.45</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2306,22 +2363,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
@@ -549,13 +549,13 @@
         <v>27.27</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -584,13 +584,13 @@
         <v>36.36</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -604,28 +604,28 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>31</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>88.56999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>11.43</v>
+        <v>8.82</v>
       </c>
       <c r="I4" s="2">
         <v>8.6</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -744,28 +744,28 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -814,28 +814,28 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>28</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H10" s="1">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -884,22 +884,22 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>91.89</v>
+        <v>91.67</v>
       </c>
       <c r="H12" s="1">
-        <v>8.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -989,10 +989,10 @@
         <v>31</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1129,22 +1129,22 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>34</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H19" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1164,22 +1164,22 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>34</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H20" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1234,28 +1234,28 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22">
         <v>24</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H22" s="1">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1324,22 +1324,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>11.36</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1356,22 +1359,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1385,25 +1391,28 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.94</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1513,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1528,7 +1537,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1577,13 +1586,13 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1592,7 +1601,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1641,25 +1650,28 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>2.78</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1676,22 +1688,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1708,22 +1723,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.6</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1737,25 +1755,28 @@
         <v>31</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F15">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.1</v>
       </c>
       <c r="J15">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1772,22 +1793,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1804,22 +1828,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1836,22 +1863,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1865,25 +1895,28 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1897,25 +1930,28 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.4</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1932,22 +1968,25 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>3.03</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J21">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1961,25 +2000,28 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2048,25 +2090,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>72.73</v>
+        <v>88.64</v>
       </c>
       <c r="H2" s="1">
-        <v>27.27</v>
+        <v>11.36</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2083,25 +2125,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>63.64</v>
+        <v>95.45</v>
       </c>
       <c r="H3" s="1">
-        <v>36.36</v>
+        <v>4.55</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2115,28 +2157,28 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>88.56999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H4" s="1">
-        <v>11.43</v>
+        <v>2.94</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2255,28 +2297,28 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2325,28 +2367,28 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>28</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H10" s="1">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2395,22 +2437,22 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>91.89</v>
+        <v>97.22</v>
       </c>
       <c r="H12" s="1">
-        <v>8.109999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2433,19 +2475,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2468,19 +2510,19 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>87.88</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2500,10 +2542,10 @@
         <v>31</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2515,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2538,19 +2580,19 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2573,19 +2615,19 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2608,19 +2650,19 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H18" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I18" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2640,22 +2682,22 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>34</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H19" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2675,22 +2717,22 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>34</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H20" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2713,19 +2755,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H21" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
       <c r="I21" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2745,28 +2787,28 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22">
         <v>24</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H22" s="1">
-        <v>17.24</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
@@ -712,25 +712,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -747,25 +747,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -829,13 +829,13 @@
         <v>6.67</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -864,13 +864,13 @@
         <v>3.13</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1429,22 +1429,25 @@
         <v>44</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1461,22 +1464,25 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1493,22 +1499,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>27.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1525,22 +1534,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>23.33</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1557,22 +1569,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1589,22 +1604,25 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1621,22 +1639,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.9</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2207,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2242,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2265,25 +2286,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>97.5</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="2">
         <v>7.5</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2300,25 +2321,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2347,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2370,25 +2391,25 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H10" s="1">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2405,25 +2426,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="H11" s="1">
-        <v>3.13</v>
+        <v>6.25</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
@@ -2111,19 +2111,19 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2146,19 +2146,19 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H3" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2181,16 +2181,16 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>9</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2461,19 +2461,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>6.25</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>5.56</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>5.56</v>
       </c>
       <c r="I20" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2776,19 +2776,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20212.xlsx
@@ -1499,25 +1499,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1534,25 +1534,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>76.67</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1">
-        <v>23.33</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1569,25 +1569,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1604,25 +1604,25 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>90</v>
+        <v>96.67</v>
       </c>
       <c r="H10" s="1">
-        <v>10</v>
+        <v>3.33</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1651,13 +1651,13 @@
         <v>6.25</v>
       </c>
       <c r="I11" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2286,19 +2286,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>3.33</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>6.25</v>
       </c>
       <c r="I11" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
